--- a/src/pages/data/data_corp_projection.xlsx
+++ b/src/pages/data/data_corp_projection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8E5B40-F9C6-4C9F-886F-2A1BAE947FD3}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4854229E-FF26-4D57-ADB2-52873B3ED594}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
   </bookViews>
   <sheets>
     <sheet name="data_mat_proj" sheetId="1" r:id="rId1"/>
@@ -587,7 +587,7 @@
         <v>2026</v>
       </c>
       <c r="C8">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -664,7 +664,7 @@
         <v>2026</v>
       </c>
       <c r="C15">
-        <v>674</v>
+        <v>686</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -741,7 +741,7 @@
         <v>2026</v>
       </c>
       <c r="C22">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -818,7 +818,7 @@
         <v>2026</v>
       </c>
       <c r="C29">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -895,7 +895,7 @@
         <v>2026</v>
       </c>
       <c r="C36">
-        <v>922</v>
+        <v>919</v>
       </c>
     </row>
   </sheetData>
@@ -930,7 +930,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -952,7 +952,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -985,7 +985,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,7 +996,7 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1029,7 +1029,7 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1040,7 +1040,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1051,7 +1051,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1062,7 +1062,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1084,7 +1084,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1095,7 +1095,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1128,7 +1128,7 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1172,7 +1172,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1183,7 +1183,7 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1194,7 +1194,7 @@
         <v>9</v>
       </c>
       <c r="C26">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
         <v>11</v>
       </c>
       <c r="C28">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1227,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1238,7 +1238,7 @@
         <v>13</v>
       </c>
       <c r="C30">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1249,7 +1249,7 @@
         <v>14</v>
       </c>
       <c r="C31">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1260,7 +1260,7 @@
         <v>18</v>
       </c>
       <c r="C32">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1271,7 +1271,7 @@
         <v>19</v>
       </c>
       <c r="C33">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1282,7 +1282,7 @@
         <v>20</v>
       </c>
       <c r="C34">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1293,7 +1293,7 @@
         <v>21</v>
       </c>
       <c r="C35">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1304,7 +1304,7 @@
         <v>18</v>
       </c>
       <c r="C36">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1315,7 +1315,7 @@
         <v>19</v>
       </c>
       <c r="C37">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
